--- a/artfynd/A 37646-2026 artfynd.xlsx
+++ b/artfynd/A 37646-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126694196</v>
+        <v>136731014</v>
       </c>
       <c r="B2" t="n">
-        <v>45044</v>
+        <v>96777</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102018</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stormosseberget, Stormosseberget, Sm</t>
+          <t>Stormosseberget, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574773</v>
+        <v>574498</v>
       </c>
       <c r="R2" t="n">
-        <v>6453505</v>
+        <v>6453472</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,79 +765,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126694196</t>
+          <t>https://artportalen.se/Sighting/136731014</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126696587</v>
+        <v>136731266</v>
       </c>
       <c r="B3" t="n">
-        <v>45044</v>
+        <v>96649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102018</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stormosseberget, Stormosseberget, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574716</v>
+        <v>574587</v>
       </c>
       <c r="R3" t="n">
-        <v>6453497</v>
+        <v>6453498</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,12 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,79 +877,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126696587</t>
+          <t>https://artportalen.se/Sighting/136731266</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126696546</v>
+        <v>136731157</v>
       </c>
       <c r="B4" t="n">
-        <v>45046</v>
+        <v>96571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102020</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stormosseberget, Stormosseberget, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574716</v>
+        <v>574581</v>
       </c>
       <c r="R4" t="n">
-        <v>6453497</v>
+        <v>6453500</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,12 +959,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,79 +989,68 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126696546</t>
+          <t>https://artportalen.se/Sighting/136731157</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126696478</v>
+        <v>136735078</v>
       </c>
       <c r="B5" t="n">
-        <v>45049</v>
+        <v>89258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102021</v>
+        <v>4373</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Sprödvaxing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Hygrocybe ceracea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Wulfen) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stormosseberget, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574716</v>
+        <v>574701</v>
       </c>
       <c r="R5" t="n">
-        <v>6453496</v>
+        <v>6453505</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,12 +1074,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,24 +1088,789 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136735078</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136735031</v>
+      </c>
+      <c r="B6" t="n">
+        <v>89263</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4379</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Toppvaxing</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hygrocybe conica</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stormosseberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>574712</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6453510</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136735031</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136735105</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93043</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4740</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sotriska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lactarius lignyotus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stormosseberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>574624</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6453481</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136735105</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126694196</v>
+      </c>
+      <c r="B8" t="n">
+        <v>45044</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102018</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bredbrämad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Zygaena lonicerae</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stormosseberget, Stormosseberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>574773</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6453505</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126694196</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126696587</v>
+      </c>
+      <c r="B9" t="n">
+        <v>45044</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102018</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bredbrämad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Zygaena lonicerae</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stormosseberget, Stormosseberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>574716</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6453497</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126696587</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126696546</v>
+      </c>
+      <c r="B10" t="n">
+        <v>45046</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102020</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Smalsprötad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Zygaena osterodensis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Reiss, 1921</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stormosseberget, Stormosseberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>574716</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6453497</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126696546</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126696478</v>
+      </c>
+      <c r="B11" t="n">
+        <v>45049</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Zygaena viciae</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stormosseberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>574716</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6453496</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/126696478</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136731891</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98425</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222736</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Majbräken</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Athyrium filix-femina</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stormosseberget, Stormosseberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>574626</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6453499</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136731891</t>
         </is>
       </c>
     </row>
@@ -1134,6 +1880,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37646-2026 artfynd.xlsx
+++ b/artfynd/A 37646-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136731014</v>
       </c>
       <c r="B2" t="n">
-        <v>96777</v>
+        <v>96782</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136731266</v>
       </c>
       <c r="B3" t="n">
-        <v>96649</v>
+        <v>96654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136731157</v>
       </c>
       <c r="B4" t="n">
-        <v>96571</v>
+        <v>96576</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136735078</v>
       </c>
       <c r="B5" t="n">
-        <v>89258</v>
+        <v>89260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136735031</v>
       </c>
       <c r="B6" t="n">
-        <v>89263</v>
+        <v>89265</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136735105</v>
       </c>
       <c r="B7" t="n">
-        <v>93043</v>
+        <v>93048</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136731891</v>
       </c>
       <c r="B12" t="n">
-        <v>98425</v>
+        <v>98430</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37646-2026 artfynd.xlsx
+++ b/artfynd/A 37646-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136731014</v>
       </c>
       <c r="B2" t="n">
-        <v>96782</v>
+        <v>96784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136731266</v>
       </c>
       <c r="B3" t="n">
-        <v>96654</v>
+        <v>96656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136731157</v>
       </c>
       <c r="B4" t="n">
-        <v>96576</v>
+        <v>96578</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136735078</v>
       </c>
       <c r="B5" t="n">
-        <v>89260</v>
+        <v>89262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136735031</v>
       </c>
       <c r="B6" t="n">
-        <v>89265</v>
+        <v>89267</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136735105</v>
       </c>
       <c r="B7" t="n">
-        <v>93048</v>
+        <v>93050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136731891</v>
       </c>
       <c r="B12" t="n">
-        <v>98430</v>
+        <v>98432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37646-2026 artfynd.xlsx
+++ b/artfynd/A 37646-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136731014</v>
       </c>
       <c r="B2" t="n">
-        <v>96784</v>
+        <v>96790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136731266</v>
       </c>
       <c r="B3" t="n">
-        <v>96656</v>
+        <v>96662</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136731157</v>
       </c>
       <c r="B4" t="n">
-        <v>96578</v>
+        <v>96584</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136735078</v>
       </c>
       <c r="B5" t="n">
-        <v>89262</v>
+        <v>89264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136735031</v>
       </c>
       <c r="B6" t="n">
-        <v>89267</v>
+        <v>89269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136735105</v>
       </c>
       <c r="B7" t="n">
-        <v>93050</v>
+        <v>93052</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136731891</v>
       </c>
       <c r="B12" t="n">
-        <v>98432</v>
+        <v>98438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37646-2026 artfynd.xlsx
+++ b/artfynd/A 37646-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136731014</v>
       </c>
       <c r="B2" t="n">
-        <v>96790</v>
+        <v>96792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136731266</v>
       </c>
       <c r="B3" t="n">
-        <v>96662</v>
+        <v>96664</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136731157</v>
       </c>
       <c r="B4" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136735078</v>
       </c>
       <c r="B5" t="n">
-        <v>89264</v>
+        <v>89266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136735031</v>
       </c>
       <c r="B6" t="n">
-        <v>89269</v>
+        <v>89271</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136735105</v>
       </c>
       <c r="B7" t="n">
-        <v>93052</v>
+        <v>93054</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136731891</v>
       </c>
       <c r="B12" t="n">
-        <v>98438</v>
+        <v>98440</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37646-2026 artfynd.xlsx
+++ b/artfynd/A 37646-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136731014</v>
       </c>
       <c r="B2" t="n">
-        <v>96792</v>
+        <v>96793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136731266</v>
       </c>
       <c r="B3" t="n">
-        <v>96664</v>
+        <v>96665</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136731157</v>
       </c>
       <c r="B4" t="n">
-        <v>96586</v>
+        <v>96587</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136735078</v>
       </c>
       <c r="B5" t="n">
-        <v>89266</v>
+        <v>89267</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136735031</v>
       </c>
       <c r="B6" t="n">
-        <v>89271</v>
+        <v>89272</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136735105</v>
       </c>
       <c r="B7" t="n">
-        <v>93054</v>
+        <v>93055</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136731891</v>
       </c>
       <c r="B12" t="n">
-        <v>98440</v>
+        <v>98441</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37646-2026 artfynd.xlsx
+++ b/artfynd/A 37646-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136731014</v>
       </c>
       <c r="B2" t="n">
-        <v>96793</v>
+        <v>96799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136731266</v>
       </c>
       <c r="B3" t="n">
-        <v>96665</v>
+        <v>96671</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136731157</v>
       </c>
       <c r="B4" t="n">
-        <v>96587</v>
+        <v>96593</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136735078</v>
       </c>
       <c r="B5" t="n">
-        <v>89267</v>
+        <v>89273</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136735031</v>
       </c>
       <c r="B6" t="n">
-        <v>89272</v>
+        <v>89278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136735105</v>
       </c>
       <c r="B7" t="n">
-        <v>93055</v>
+        <v>93061</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136731891</v>
       </c>
       <c r="B12" t="n">
-        <v>98441</v>
+        <v>98447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37646-2026 artfynd.xlsx
+++ b/artfynd/A 37646-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136731014</v>
       </c>
       <c r="B2" t="n">
-        <v>96799</v>
+        <v>96803</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136731266</v>
       </c>
       <c r="B3" t="n">
-        <v>96671</v>
+        <v>96675</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136731157</v>
       </c>
       <c r="B4" t="n">
-        <v>96593</v>
+        <v>96597</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136735078</v>
       </c>
       <c r="B5" t="n">
-        <v>89273</v>
+        <v>89277</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136735031</v>
       </c>
       <c r="B6" t="n">
-        <v>89278</v>
+        <v>89282</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136735105</v>
       </c>
       <c r="B7" t="n">
-        <v>93061</v>
+        <v>93065</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136731891</v>
       </c>
       <c r="B12" t="n">
-        <v>98447</v>
+        <v>98451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37646-2026 artfynd.xlsx
+++ b/artfynd/A 37646-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136731014</v>
       </c>
       <c r="B2" t="n">
-        <v>96803</v>
+        <v>96805</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136731266</v>
       </c>
       <c r="B3" t="n">
-        <v>96675</v>
+        <v>96677</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136731157</v>
       </c>
       <c r="B4" t="n">
-        <v>96597</v>
+        <v>96599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136731891</v>
       </c>
       <c r="B12" t="n">
-        <v>98451</v>
+        <v>98453</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37646-2026 artfynd.xlsx
+++ b/artfynd/A 37646-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136731014</v>
       </c>
       <c r="B2" t="n">
-        <v>96805</v>
+        <v>96807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136731266</v>
       </c>
       <c r="B3" t="n">
-        <v>96677</v>
+        <v>96679</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136731157</v>
       </c>
       <c r="B4" t="n">
-        <v>96599</v>
+        <v>96601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136735078</v>
       </c>
       <c r="B5" t="n">
-        <v>89277</v>
+        <v>89279</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136735031</v>
       </c>
       <c r="B6" t="n">
-        <v>89282</v>
+        <v>89284</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136735105</v>
       </c>
       <c r="B7" t="n">
-        <v>93065</v>
+        <v>93067</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136731891</v>
       </c>
       <c r="B12" t="n">
-        <v>98453</v>
+        <v>98455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37646-2026 artfynd.xlsx
+++ b/artfynd/A 37646-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136731014</v>
       </c>
       <c r="B2" t="n">
-        <v>96807</v>
+        <v>96820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136731266</v>
       </c>
       <c r="B3" t="n">
-        <v>96679</v>
+        <v>96692</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136731157</v>
       </c>
       <c r="B4" t="n">
-        <v>96601</v>
+        <v>96614</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136735078</v>
       </c>
       <c r="B5" t="n">
-        <v>89279</v>
+        <v>89292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136735031</v>
       </c>
       <c r="B6" t="n">
-        <v>89284</v>
+        <v>89297</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136735105</v>
       </c>
       <c r="B7" t="n">
-        <v>93067</v>
+        <v>93080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136731891</v>
       </c>
       <c r="B12" t="n">
-        <v>98455</v>
+        <v>98468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37646-2026 artfynd.xlsx
+++ b/artfynd/A 37646-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136731014</v>
       </c>
       <c r="B2" t="n">
-        <v>96820</v>
+        <v>96822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136731266</v>
       </c>
       <c r="B3" t="n">
-        <v>96692</v>
+        <v>96694</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136731157</v>
       </c>
       <c r="B4" t="n">
-        <v>96614</v>
+        <v>96616</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136735078</v>
       </c>
       <c r="B5" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136735031</v>
       </c>
       <c r="B6" t="n">
-        <v>89297</v>
+        <v>89299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136735105</v>
       </c>
       <c r="B7" t="n">
-        <v>93080</v>
+        <v>93082</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136731891</v>
       </c>
       <c r="B12" t="n">
-        <v>98468</v>
+        <v>98470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37646-2026 artfynd.xlsx
+++ b/artfynd/A 37646-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136731014</v>
       </c>
       <c r="B2" t="n">
-        <v>96822</v>
+        <v>96825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136731266</v>
       </c>
       <c r="B3" t="n">
-        <v>96694</v>
+        <v>96697</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136731157</v>
       </c>
       <c r="B4" t="n">
-        <v>96616</v>
+        <v>96619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136735078</v>
       </c>
       <c r="B5" t="n">
-        <v>89294</v>
+        <v>89297</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136735031</v>
       </c>
       <c r="B6" t="n">
-        <v>89299</v>
+        <v>89302</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136735105</v>
       </c>
       <c r="B7" t="n">
-        <v>93082</v>
+        <v>93085</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136731891</v>
       </c>
       <c r="B12" t="n">
-        <v>98470</v>
+        <v>98473</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37646-2026 artfynd.xlsx
+++ b/artfynd/A 37646-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136731014</v>
       </c>
       <c r="B2" t="n">
-        <v>96825</v>
+        <v>96835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136731266</v>
       </c>
       <c r="B3" t="n">
-        <v>96697</v>
+        <v>96707</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136731157</v>
       </c>
       <c r="B4" t="n">
-        <v>96619</v>
+        <v>96629</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136735078</v>
       </c>
       <c r="B5" t="n">
-        <v>89297</v>
+        <v>89307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136735031</v>
       </c>
       <c r="B6" t="n">
-        <v>89302</v>
+        <v>89312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136735105</v>
       </c>
       <c r="B7" t="n">
-        <v>93085</v>
+        <v>93095</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136731891</v>
       </c>
       <c r="B12" t="n">
-        <v>98473</v>
+        <v>98483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37646-2026 artfynd.xlsx
+++ b/artfynd/A 37646-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136731014</v>
       </c>
       <c r="B2" t="n">
-        <v>96835</v>
+        <v>96836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136731266</v>
       </c>
       <c r="B3" t="n">
-        <v>96707</v>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136731157</v>
       </c>
       <c r="B4" t="n">
-        <v>96629</v>
+        <v>96630</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136735078</v>
       </c>
       <c r="B5" t="n">
-        <v>89307</v>
+        <v>89308</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136735031</v>
       </c>
       <c r="B6" t="n">
-        <v>89312</v>
+        <v>89313</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136735105</v>
       </c>
       <c r="B7" t="n">
-        <v>93095</v>
+        <v>93096</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136731891</v>
       </c>
       <c r="B12" t="n">
-        <v>98483</v>
+        <v>98484</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
